--- a/outputs/experiment_summary.xlsx
+++ b/outputs/experiment_summary.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="302" documentId="8_{9F3B95F0-30DB-4515-9B97-03DF3D533851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CC8C6CB-F924-437F-B338-BD6179AF86B0}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="15970" windowHeight="13770" firstSheet="3" activeTab="4" xr2:uid="{171E4B5A-8144-4169-912D-E36E47E49E6C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{171E4B5A-8144-4169-912D-E36E47E49E6C}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="1" r:id="rId1"/>
